--- a/workbooks/methodology/weight_discrimination.xlsx
+++ b/workbooks/methodology/weight_discrimination.xlsx
@@ -508,10 +508,10 @@
         <v>0.0635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2512</v>
+        <v>0.251</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0488</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="3">
@@ -549,10 +549,10 @@
         <v>0.0503</v>
       </c>
       <c r="J3" t="n">
-        <v>0.199</v>
+        <v>0.1988</v>
       </c>
       <c r="K3" t="n">
-        <v>0.151</v>
+        <v>0.1512</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4265</v>
+        <v>0.4275</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0853</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3374</v>
+        <v>0.3379</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1374</v>
+        <v>-0.1379</v>
       </c>
     </row>
     <row r="5">
@@ -631,10 +631,10 @@
         <v>0.0537</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2124</v>
+        <v>0.2122</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0624</v>
+        <v>-0.0622</v>
       </c>
     </row>
     <row r="6">
@@ -1000,10 +1000,10 @@
         <v>0.108</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3014</v>
+        <v>0.3007</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0014</v>
+        <v>-0.0007</v>
       </c>
     </row>
     <row r="15">
@@ -1041,10 +1041,10 @@
         <v>0.1281</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3575</v>
+        <v>0.3567</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0075</v>
+        <v>-0.0067</v>
       </c>
     </row>
     <row r="16">
@@ -1073,19 +1073,19 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3442</v>
+        <v>0.3481</v>
       </c>
       <c r="H16" t="n">
         <v>0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0688</v>
+        <v>0.0696</v>
       </c>
       <c r="J16" t="n">
-        <v>0.192</v>
+        <v>0.1938</v>
       </c>
       <c r="K16" t="n">
-        <v>0.008</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="17">
@@ -1123,10 +1123,10 @@
         <v>0.0535</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1493</v>
+        <v>0.149</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0007</v>
+        <v>0.001</v>
       </c>
     </row>
   </sheetData>

--- a/workbooks/methodology/weight_discrimination.xlsx
+++ b/workbooks/methodology/weight_discrimination.xlsx
@@ -496,22 +496,22 @@
         <v>285</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2118</v>
+        <v>0.2162</v>
       </c>
       <c r="H2" t="n">
         <v>0.85</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0635</v>
+        <v>0.0649</v>
       </c>
       <c r="J2" t="n">
-        <v>0.251</v>
+        <v>0.2526</v>
       </c>
       <c r="K2" t="n">
-        <v>0.049</v>
+        <v>0.0474</v>
       </c>
     </row>
     <row r="3">
@@ -537,22 +537,22 @@
         <v>285</v>
       </c>
       <c r="F3" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1438</v>
+        <v>0.1475</v>
       </c>
       <c r="H3" t="n">
         <v>0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0503</v>
+        <v>0.0516</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1988</v>
+        <v>0.2009</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1512</v>
+        <v>0.1491</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4275</v>
+        <v>0.4385</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0877</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3379</v>
+        <v>0.3414</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1379</v>
+        <v>-0.1414</v>
       </c>
     </row>
     <row r="5">
@@ -619,22 +619,22 @@
         <v>285</v>
       </c>
       <c r="F5" t="n">
-        <v>16.5</v>
+        <v>17.9</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3578</v>
+        <v>0.3513</v>
       </c>
       <c r="H5" t="n">
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0537</v>
+        <v>0.0527</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2122</v>
+        <v>0.2051</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0622</v>
+        <v>-0.0551</v>
       </c>
     </row>
     <row r="6">
@@ -660,22 +660,22 @@
         <v>105</v>
       </c>
       <c r="F6" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0914</v>
+        <v>0.1042</v>
       </c>
       <c r="H6" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0274</v>
+        <v>0.0313</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1717</v>
+        <v>0.1842</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1283</v>
+        <v>0.1158</v>
       </c>
     </row>
     <row r="7">
@@ -701,22 +701,22 @@
         <v>105</v>
       </c>
       <c r="F7" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.1005</v>
       </c>
       <c r="H7" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0316</v>
+        <v>0.0352</v>
       </c>
       <c r="J7" t="n">
-        <v>0.198</v>
+        <v>0.2072</v>
       </c>
       <c r="K7" t="n">
-        <v>0.152</v>
+        <v>0.1428</v>
       </c>
     </row>
     <row r="8">
@@ -745,19 +745,19 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.429</v>
+        <v>0.4589</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0858</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5377</v>
+        <v>0.5402</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3377</v>
+        <v>-0.3402</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>44.8</v>
+        <v>48.6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.098</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0147</v>
+        <v>0.0117</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0921</v>
+        <v>0.0689</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0579</v>
+        <v>0.08110000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -824,22 +824,22 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2196</v>
+        <v>0.2206</v>
       </c>
       <c r="H10" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0659</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2475</v>
+        <v>0.2483</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0525</v>
+        <v>0.0517</v>
       </c>
     </row>
     <row r="11">
@@ -918,10 +918,10 @@
         <v>0.0979</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3677</v>
+        <v>0.3672</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1677</v>
+        <v>-0.1672</v>
       </c>
     </row>
     <row r="13">
@@ -959,10 +959,10 @@
         <v>0.0948</v>
       </c>
       <c r="J13" t="n">
-        <v>0.356</v>
+        <v>0.3556</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.206</v>
+        <v>-0.2056</v>
       </c>
     </row>
     <row r="14">
@@ -991,19 +991,19 @@
         <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.36</v>
+        <v>0.3579</v>
       </c>
       <c r="H14" t="n">
         <v>0.85</v>
       </c>
       <c r="I14" t="n">
-        <v>0.108</v>
+        <v>0.1074</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3007</v>
+        <v>0.2992</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0007</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="15">
@@ -1041,10 +1041,10 @@
         <v>0.1281</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3567</v>
+        <v>0.3569</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0067</v>
+        <v>-0.0069</v>
       </c>
     </row>
     <row r="16">
@@ -1082,10 +1082,10 @@
         <v>0.0696</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1938</v>
+        <v>0.1939</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0062</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="17">
@@ -1114,19 +1114,19 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3564</v>
+        <v>0.3593</v>
       </c>
       <c r="H17" t="n">
         <v>0.58</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0535</v>
+        <v>0.0539</v>
       </c>
       <c r="J17" t="n">
-        <v>0.149</v>
+        <v>0.1502</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001</v>
+        <v>-0.0002</v>
       </c>
     </row>
   </sheetData>
